--- a/xgb_classification_train_results.xlsx
+++ b/xgb_classification_train_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,10 +458,10 @@
         <v>0.9379474940334129</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9379399856188521</v>
+        <v>0.9374301816175524</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9379655237193627</v>
+        <v>0.9374457165316</v>
       </c>
       <c r="D2" t="n">
         <v>0.1</v>
@@ -473,29 +473,6 @@
         <v>150</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>0.9284009546539379</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0.9283085541083602</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.9283604110800084</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F3" t="n">
-        <v>150</v>
-      </c>
-      <c r="G3" t="n">
         <v>0.8</v>
       </c>
     </row>
